--- a/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>FNWB</t>
   </si>
@@ -656,112 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42916</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42551</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42185</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41820</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41455</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41090</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100900</v>
+      </c>
+      <c r="E8" s="3">
         <v>80400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>63700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>51700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>49300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>45800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>36800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>27500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>26600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26900</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -801,9 +807,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,9 +961,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,9 +1006,12 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E17" s="3">
         <v>12100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E18" s="3">
         <v>68300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>56900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>44000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>35600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>22900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11800</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,92 +1179,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-52000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-38800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-30700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-26100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-26900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-13100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-23600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-21700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-28300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15600</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E21" s="3">
         <v>18400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>4900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1272,93 +1311,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>16300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3800</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1800</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>13500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>15500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1542,15 +1602,15 @@
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-1100</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E32" s="3">
         <v>52000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>38800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>30700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>26100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>26900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>13100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>23600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>21700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>28300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15600</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>15500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>15500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42916</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42551</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42185</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41820</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41455</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41090</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,73 +1987,77 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E41" s="3">
         <v>17100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13900</v>
-      </c>
-      <c r="F41" s="3">
-        <v>13500</v>
       </c>
       <c r="G41" s="3">
         <v>13500</v>
       </c>
       <c r="H41" s="3">
+        <v>13500</v>
+      </c>
+      <c r="I41" s="3">
         <v>15400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14500</v>
-      </c>
-      <c r="K41" s="3">
-        <v>12800</v>
       </c>
       <c r="L41" s="3">
         <v>12800</v>
       </c>
       <c r="M41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="N41" s="3">
         <v>14200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>131800</v>
+      </c>
+      <c r="E42" s="3">
         <v>54500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>117300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>57600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>41300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30000</v>
-      </c>
-      <c r="J42" s="3">
-        <v>14200</v>
       </c>
       <c r="K42" s="3">
         <v>14200</v>
@@ -1977,17 +2066,20 @@
         <v>14200</v>
       </c>
       <c r="M42" s="3">
+        <v>14200</v>
+      </c>
+      <c r="N42" s="3">
         <v>14800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>20600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>40900</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,9 +2164,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2111,9 +2209,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2153,9 +2254,12 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2195,74 +2299,80 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E48" s="3">
         <v>24800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>13500</v>
       </c>
       <c r="L48" s="3">
         <v>13500</v>
       </c>
       <c r="M48" s="3">
+        <v>13500</v>
+      </c>
+      <c r="N48" s="3">
         <v>12300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E49" s="3">
         <v>5000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1100</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1000</v>
       </c>
       <c r="K49" s="3">
         <v>1000</v>
@@ -2271,17 +2381,20 @@
         <v>1000</v>
       </c>
       <c r="M49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N49" s="3">
         <v>1300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,18 +2479,21 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E52" s="3">
         <v>14100</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2390,8 +2509,8 @@
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2201800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2042100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1921100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1654300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1307300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1258800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1215700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1087700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1010100</v>
       </c>
       <c r="L54" s="3">
         <v>1010100</v>
       </c>
       <c r="M54" s="3">
+        <v>1010100</v>
+      </c>
+      <c r="N54" s="3">
         <v>795300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>784500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>771900</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,31 +2655,32 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
@@ -2559,7 +2689,7 @@
         <v>200</v>
       </c>
       <c r="M57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>300</v>
@@ -2567,9 +2697,12 @@
       <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2609,51 +2742,57 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E59" s="3">
         <v>32300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>15200</v>
       </c>
       <c r="L59" s="3">
         <v>15200</v>
       </c>
       <c r="M59" s="3">
+        <v>15200</v>
+      </c>
+      <c r="N59" s="3">
         <v>6400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2693,9 +2832,12 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2703,11 +2845,11 @@
         <v>39400</v>
       </c>
       <c r="E61" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F61" s="3">
         <v>39300</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -2735,9 +2877,12 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2769,17 +2914,20 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2900</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2038500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1880500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1730100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1468000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1130500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1086500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1038600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>910000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>820400</v>
       </c>
       <c r="L66" s="3">
         <v>820400</v>
       </c>
       <c r="M66" s="3">
+        <v>820400</v>
+      </c>
+      <c r="N66" s="3">
         <v>714300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>705900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>694600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E72" s="3">
         <v>114400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>103000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>92700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>86200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>81600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>78600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>77500</v>
-      </c>
-      <c r="K72" s="3">
-        <v>77300</v>
       </c>
       <c r="L72" s="3">
         <v>77300</v>
       </c>
       <c r="M72" s="3">
+        <v>77300</v>
+      </c>
+      <c r="N72" s="3">
         <v>79700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>77000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>74700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E76" s="3">
         <v>161600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>191000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>186400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>176900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>172300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>177000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>177700</v>
-      </c>
-      <c r="K76" s="3">
-        <v>189700</v>
       </c>
       <c r="L76" s="3">
         <v>189700</v>
       </c>
       <c r="M76" s="3">
+        <v>189700</v>
+      </c>
+      <c r="N76" s="3">
         <v>81000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>78600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>77300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42916</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42551</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42185</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41820</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41455</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41090</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>15500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1600</v>
       </c>
       <c r="H83" s="3">
         <v>1600</v>
       </c>
       <c r="I83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>2300</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E89" s="3">
         <v>15900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1200</v>
       </c>
       <c r="L89" s="3">
         <v>-1200</v>
       </c>
       <c r="M89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N89" s="3">
         <v>3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9900</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-1300</v>
       </c>
       <c r="L91" s="3">
         <v>-1300</v>
       </c>
       <c r="M91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-84200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-237600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-136900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-316000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-60700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-118000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-80300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-18400</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-24100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,29 +4221,30 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-300</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,51 +4398,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>143900</v>
+      </c>
+      <c r="E100" s="3">
         <v>141300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>182600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>319100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>28300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>125500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>80800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>10800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>20900</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4225,64 +4473,70 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-80400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>60900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1600</v>
-      </c>
-      <c r="K102" s="3">
-        <v>26100</v>
       </c>
       <c r="L102" s="3">
         <v>26100</v>
       </c>
       <c r="M102" s="3">
+        <v>26100</v>
+      </c>
+      <c r="N102" s="3">
         <v>-4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>FNWB</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>100900</v>
+        <v>64100</v>
       </c>
       <c r="E8" s="3">
-        <v>80400</v>
+        <v>77200</v>
       </c>
       <c r="F8" s="3">
-        <v>63700</v>
+        <v>72600</v>
       </c>
       <c r="G8" s="3">
-        <v>51700</v>
+        <v>54800</v>
       </c>
       <c r="H8" s="3">
-        <v>49300</v>
+        <v>44200</v>
       </c>
       <c r="I8" s="3">
-        <v>45800</v>
+        <v>41500</v>
       </c>
       <c r="J8" s="3">
-        <v>20300</v>
+        <v>38600</v>
       </c>
       <c r="K8" s="3">
         <v>36800</v>
@@ -816,26 +816,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>77200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>72600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>54800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>44200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>41500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>38600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -970,26 +970,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>-1500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>40800</v>
+        <v>60100</v>
       </c>
       <c r="E17" s="3">
-        <v>12100</v>
+        <v>61400</v>
       </c>
       <c r="F17" s="3">
-        <v>6700</v>
+        <v>53700</v>
       </c>
       <c r="G17" s="3">
-        <v>7700</v>
+        <v>41000</v>
       </c>
       <c r="H17" s="3">
-        <v>12100</v>
+        <v>32700</v>
       </c>
       <c r="I17" s="3">
-        <v>10200</v>
+        <v>32600</v>
       </c>
       <c r="J17" s="3">
-        <v>3500</v>
+        <v>31300</v>
       </c>
       <c r="K17" s="3">
         <v>6400</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>60100</v>
+        <v>4000</v>
       </c>
       <c r="E18" s="3">
-        <v>68300</v>
+        <v>15700</v>
       </c>
       <c r="F18" s="3">
-        <v>56900</v>
+        <v>18900</v>
       </c>
       <c r="G18" s="3">
-        <v>44000</v>
+        <v>13700</v>
       </c>
       <c r="H18" s="3">
-        <v>37200</v>
+        <v>11500</v>
       </c>
       <c r="I18" s="3">
-        <v>35600</v>
+        <v>9000</v>
       </c>
       <c r="J18" s="3">
-        <v>16800</v>
+        <v>7300</v>
       </c>
       <c r="K18" s="3">
         <v>30400</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-57400</v>
+        <v>1400</v>
       </c>
       <c r="E20" s="3">
-        <v>-52000</v>
+        <v>900</v>
       </c>
       <c r="F20" s="3">
-        <v>-38800</v>
+        <v>800</v>
       </c>
       <c r="G20" s="3">
-        <v>-30700</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>-26100</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>-26900</v>
+        <v>300</v>
       </c>
       <c r="J20" s="3">
-        <v>-13100</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>-23600</v>
@@ -1234,22 +1234,22 @@
         <v>4300</v>
       </c>
       <c r="E21" s="3">
-        <v>18400</v>
+        <v>16900</v>
       </c>
       <c r="F21" s="3">
-        <v>19600</v>
+        <v>19700</v>
       </c>
       <c r="G21" s="3">
-        <v>14900</v>
+        <v>15200</v>
       </c>
       <c r="H21" s="3">
-        <v>12700</v>
+        <v>13000</v>
       </c>
       <c r="I21" s="3">
         <v>10300</v>
       </c>
       <c r="J21" s="3">
-        <v>4300</v>
+        <v>8500</v>
       </c>
       <c r="K21" s="3">
         <v>8300</v>
@@ -1275,26 +1275,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>8700</v>
       </c>
       <c r="J23" s="3">
-        <v>3700</v>
+        <v>7800</v>
       </c>
       <c r="K23" s="3">
         <v>6800</v>
@@ -1384,7 +1384,7 @@
         <v>1600</v>
       </c>
       <c r="J24" s="3">
-        <v>1000</v>
+        <v>2900</v>
       </c>
       <c r="K24" s="3">
         <v>1700</v>
@@ -1474,7 +1474,7 @@
         <v>7100</v>
       </c>
       <c r="J26" s="3">
-        <v>2800</v>
+        <v>4900</v>
       </c>
       <c r="K26" s="3">
         <v>5100</v>
@@ -1510,7 +1510,7 @@
         <v>14900</v>
       </c>
       <c r="G27" s="3">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="H27" s="3">
         <v>9000</v>
@@ -1519,7 +1519,7 @@
         <v>7100</v>
       </c>
       <c r="J27" s="3">
-        <v>2800</v>
+        <v>4900</v>
       </c>
       <c r="K27" s="3">
         <v>5100</v>
@@ -1590,26 +1590,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>57400</v>
+        <v>-1400</v>
       </c>
       <c r="E32" s="3">
-        <v>52000</v>
+        <v>-900</v>
       </c>
       <c r="F32" s="3">
-        <v>38800</v>
+        <v>-800</v>
       </c>
       <c r="G32" s="3">
-        <v>30700</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>26100</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>26900</v>
+        <v>-300</v>
       </c>
       <c r="J32" s="3">
-        <v>13100</v>
+        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>23600</v>
@@ -1774,13 +1774,13 @@
         <v>2300</v>
       </c>
       <c r="E33" s="3">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="F33" s="3">
-        <v>14900</v>
+        <v>15400</v>
       </c>
       <c r="G33" s="3">
-        <v>10000</v>
+        <v>10300</v>
       </c>
       <c r="H33" s="3">
         <v>9000</v>
@@ -1789,7 +1789,7 @@
         <v>7100</v>
       </c>
       <c r="J33" s="3">
-        <v>1700</v>
+        <v>4900</v>
       </c>
       <c r="K33" s="3">
         <v>5100</v>
@@ -1864,13 +1864,13 @@
         <v>2300</v>
       </c>
       <c r="E35" s="3">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="F35" s="3">
-        <v>14900</v>
+        <v>15400</v>
       </c>
       <c r="G35" s="3">
-        <v>10000</v>
+        <v>10300</v>
       </c>
       <c r="H35" s="3">
         <v>9000</v>
@@ -1879,7 +1879,7 @@
         <v>7100</v>
       </c>
       <c r="J35" s="3">
-        <v>1700</v>
+        <v>4900</v>
       </c>
       <c r="K35" s="3">
         <v>5100</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19800</v>
+        <v>123200</v>
       </c>
       <c r="E41" s="3">
-        <v>17100</v>
+        <v>45600</v>
       </c>
       <c r="F41" s="3">
-        <v>13900</v>
+        <v>126000</v>
       </c>
       <c r="G41" s="3">
-        <v>13500</v>
+        <v>65200</v>
       </c>
       <c r="H41" s="3">
-        <v>13500</v>
+        <v>37900</v>
       </c>
       <c r="I41" s="3">
-        <v>15400</v>
+        <v>17200</v>
       </c>
       <c r="J41" s="3">
-        <v>13800</v>
+        <v>26700</v>
       </c>
       <c r="K41" s="3">
         <v>14500</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>131800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>54500</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>117300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>57600</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>41300</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>17800</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>14200</v>
@@ -2083,26 +2083,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2128,23 +2128,23 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G44" s="3">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>152600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>81300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>152700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>86800</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>45600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>324100</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>352500</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>353000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>370300</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>321600</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>313400</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>347400</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2312,13 +2312,13 @@
         <v>24100</v>
       </c>
       <c r="E48" s="3">
-        <v>24800</v>
+        <v>18100</v>
       </c>
       <c r="F48" s="3">
         <v>19800</v>
       </c>
       <c r="G48" s="3">
-        <v>18700</v>
+        <v>14800</v>
       </c>
       <c r="H48" s="3">
         <v>14300</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13000</v>
+        <v>40600</v>
       </c>
       <c r="E52" s="3">
-        <v>14100</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
+        <v>39700</v>
+      </c>
+      <c r="F52" s="3">
+        <v>39300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>38400</v>
+      </c>
+      <c r="H52" s="3">
+        <v>30000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J52" s="3">
+        <v>28700</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3400</v>
+        <v>1676900</v>
       </c>
       <c r="E57" s="3">
-        <v>500</v>
+        <v>1564300</v>
       </c>
       <c r="F57" s="3">
-        <v>400</v>
+        <v>1580600</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>1333500</v>
       </c>
       <c r="H57" s="3">
-        <v>400</v>
+        <v>1001600</v>
       </c>
       <c r="I57" s="3">
-        <v>500</v>
+        <v>940300</v>
       </c>
       <c r="J57" s="3">
-        <v>300</v>
+        <v>885000</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>202400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>167000</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>92900</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>91600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>84100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>36000</v>
+        <v>1300</v>
       </c>
       <c r="E59" s="3">
-        <v>32300</v>
+        <v>1400</v>
       </c>
       <c r="F59" s="3">
-        <v>29200</v>
+        <v>1100</v>
       </c>
       <c r="G59" s="3">
-        <v>23300</v>
+        <v>1100</v>
       </c>
       <c r="H59" s="3">
-        <v>14400</v>
+        <v>1100</v>
       </c>
       <c r="I59" s="3">
-        <v>8100</v>
+        <v>1100</v>
       </c>
       <c r="J59" s="3">
-        <v>7900</v>
+        <v>1200</v>
       </c>
       <c r="K59" s="3">
         <v>7400</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1913500</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1764400</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1611300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1418000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1110500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1041500</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>978600</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>39400</v>
+        <v>125000</v>
       </c>
       <c r="E61" s="3">
-        <v>39400</v>
+        <v>119400</v>
       </c>
       <c r="F61" s="3">
-        <v>39300</v>
+        <v>119300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2886,8 +2886,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -3070,10 +3070,10 @@
         <v>2038500</v>
       </c>
       <c r="E66" s="3">
-        <v>1880500</v>
+        <v>1883800</v>
       </c>
       <c r="F66" s="3">
-        <v>1730100</v>
+        <v>1730600</v>
       </c>
       <c r="G66" s="3">
         <v>1468000</v>
@@ -3634,13 +3634,13 @@
         <v>2300</v>
       </c>
       <c r="E81" s="3">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="F81" s="3">
-        <v>14900</v>
+        <v>15400</v>
       </c>
       <c r="G81" s="3">
-        <v>10000</v>
+        <v>10300</v>
       </c>
       <c r="H81" s="3">
         <v>9000</v>
@@ -3649,7 +3649,7 @@
         <v>7100</v>
       </c>
       <c r="J81" s="3">
-        <v>1700</v>
+        <v>4900</v>
       </c>
       <c r="K81" s="3">
         <v>5100</v>
@@ -3698,22 +3698,22 @@
         <v>1600</v>
       </c>
       <c r="E83" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="F83" s="3">
         <v>1400</v>
       </c>
       <c r="G83" s="3">
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="H83" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="I83" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="K83" s="3">
         <v>1500</v>
@@ -3983,7 +3983,7 @@
         <v>13300</v>
       </c>
       <c r="J89" s="3">
-        <v>5000</v>
+        <v>10400</v>
       </c>
       <c r="K89" s="3">
         <v>1100</v>
@@ -4228,22 +4228,22 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2700</v>
+        <v>2700</v>
       </c>
       <c r="E96" s="3">
-        <v>-2800</v>
+        <v>2800</v>
       </c>
       <c r="F96" s="3">
-        <v>-2500</v>
+        <v>2500</v>
       </c>
       <c r="G96" s="3">
-        <v>-2200</v>
+        <v>2200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1400</v>
+        <v>1400</v>
       </c>
       <c r="I96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>36900</v>
       </c>
       <c r="J100" s="3">
-        <v>125500</v>
+        <v>162600</v>
       </c>
       <c r="K100" s="3">
         <v>80800</v>
@@ -4452,26 +4452,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>-10500</v>
       </c>
       <c r="J102" s="3">
-        <v>12500</v>
+        <v>55000</v>
       </c>
       <c r="K102" s="3">
         <v>1600</v>

--- a/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>FNWB</t>
   </si>
@@ -656,118 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42916</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42551</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42185</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41820</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41455</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41090</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E8" s="3">
         <v>64100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>77200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>72600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>54800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>44200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>41500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>36800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>27500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>26900</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -810,36 +816,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E10" s="3">
         <v>64100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>77200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>72600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>54800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>44200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>41500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>38600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,36 +980,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
         <v>-1500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>-800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1009,36 +1028,39 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1600</v>
       </c>
       <c r="I15" s="3">
         <v>1600</v>
       </c>
       <c r="J15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K15" s="3">
         <v>1400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E17" s="3">
         <v>60100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>61400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>53700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>31300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E18" s="3">
         <v>4000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>30400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>20500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11800</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,98 +1212,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-23600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-21700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-28300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E21" s="3">
         <v>4300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>16900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>4900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1296,8 +1335,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1314,99 +1353,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1671,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>23600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>21700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>28300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15600</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42916</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42551</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42185</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41820</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41455</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41090</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,53 +2073,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E41" s="3">
         <v>123200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>126000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>65200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14500</v>
-      </c>
-      <c r="L41" s="3">
-        <v>12800</v>
       </c>
       <c r="M41" s="3">
         <v>12800</v>
       </c>
       <c r="N41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="O41" s="3">
         <v>14200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2060,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
-        <v>14200</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>14200</v>
@@ -2069,17 +2158,20 @@
         <v>14200</v>
       </c>
       <c r="N42" s="3">
+        <v>14200</v>
+      </c>
+      <c r="O42" s="3">
         <v>14800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>40900</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2104,8 +2196,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2122,9 +2214,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2137,18 +2232,18 @@
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
@@ -2167,36 +2262,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E45" s="3">
         <v>7900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3700</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2212,36 +2310,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>102400</v>
+      </c>
+      <c r="E46" s="3">
         <v>152600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>81300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>152700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>86800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>62000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>45600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2257,36 +2358,39 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>368000</v>
+      </c>
+      <c r="E47" s="3">
         <v>324100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>352500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>353000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>370300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>321600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>313400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>347400</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2302,80 +2406,86 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E48" s="3">
         <v>24100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>13500</v>
       </c>
       <c r="M48" s="3">
         <v>13500</v>
       </c>
       <c r="N48" s="3">
+        <v>13500</v>
+      </c>
+      <c r="O48" s="3">
         <v>12300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E49" s="3">
         <v>4900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1100</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1000</v>
       </c>
       <c r="L49" s="3">
         <v>1000</v>
@@ -2384,17 +2494,20 @@
         <v>1000</v>
       </c>
       <c r="N49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O49" s="3">
         <v>1300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,38 +2598,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E52" s="3">
         <v>40600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28700</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2232000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2201800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2042100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1921100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1654300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1307300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1258800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1215700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1087700</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1010100</v>
       </c>
       <c r="M54" s="3">
         <v>1010100</v>
       </c>
       <c r="N54" s="3">
+        <v>1010100</v>
+      </c>
+      <c r="O54" s="3">
         <v>795300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>784500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>771900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,34 +2785,35 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1688000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1676900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1564300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1580600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1333500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1001600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>940300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>885000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
@@ -2692,7 +2822,7 @@
         <v>200</v>
       </c>
       <c r="N57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O57" s="3">
         <v>300</v>
@@ -2700,36 +2830,39 @@
       <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>300</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>202400</v>
+        <v>138900</v>
       </c>
       <c r="E58" s="3">
+        <v>202500</v>
+      </c>
+      <c r="F58" s="3">
         <v>167000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>60000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>92900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>91600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>84100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2745,20 +2878,23 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1100</v>
       </c>
       <c r="G59" s="3">
         <v>1100</v>
@@ -2770,56 +2906,59 @@
         <v>1100</v>
       </c>
       <c r="J59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>15200</v>
       </c>
       <c r="M59" s="3">
         <v>15200</v>
       </c>
       <c r="N59" s="3">
+        <v>15200</v>
+      </c>
+      <c r="O59" s="3">
         <v>6400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1913500</v>
+        <v>1862800</v>
       </c>
       <c r="E60" s="3">
+        <v>1911800</v>
+      </c>
+      <c r="F60" s="3">
         <v>1764400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1611300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1418000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1110500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1041500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>978600</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2835,36 +2974,39 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>125000</v>
+        <v>214700</v>
       </c>
       <c r="E61" s="3">
+        <v>125900</v>
+      </c>
+      <c r="F61" s="3">
         <v>119400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>119300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>50000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>45000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>60000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2880,17 +3022,20 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -2917,17 +3062,20 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>1100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2900</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2078100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2038500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1883800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1730600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1468000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1130500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1086500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1038600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>910000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>820400</v>
       </c>
       <c r="M66" s="3">
         <v>820400</v>
       </c>
       <c r="N66" s="3">
+        <v>820400</v>
+      </c>
+      <c r="O66" s="3">
         <v>714300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>705900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>694600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>97200</v>
+      </c>
+      <c r="E72" s="3">
         <v>107300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>114400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>103000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>92700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>86200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>81600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>78600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>77500</v>
-      </c>
-      <c r="L72" s="3">
-        <v>77300</v>
       </c>
       <c r="M72" s="3">
         <v>77300</v>
       </c>
       <c r="N72" s="3">
+        <v>77300</v>
+      </c>
+      <c r="O72" s="3">
         <v>79700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>77000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>74700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>153900</v>
+      </c>
+      <c r="E76" s="3">
         <v>163300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>161600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>191000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>186400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>176900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>172300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>177000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>177700</v>
-      </c>
-      <c r="L76" s="3">
-        <v>189700</v>
       </c>
       <c r="M76" s="3">
         <v>189700</v>
       </c>
       <c r="N76" s="3">
+        <v>189700</v>
+      </c>
+      <c r="O76" s="3">
         <v>81000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>78600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>77300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42916</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42551</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42185</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41820</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41455</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41090</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1400</v>
       </c>
       <c r="G83" s="3">
         <v>1400</v>
       </c>
       <c r="H83" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="I83" s="3">
         <v>1300</v>
       </c>
       <c r="J83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2300</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E89" s="3">
         <v>17900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1100</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-1200</v>
       </c>
       <c r="M89" s="3">
         <v>-1200</v>
       </c>
       <c r="N89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O89" s="3">
         <v>3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9900</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1300</v>
       </c>
       <c r="M91" s="3">
         <v>-1300</v>
       </c>
       <c r="N91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-87100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-84200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-237600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-136900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-316000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-60700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-118000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-80300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>-18400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,32 +4454,33 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E96" s="3">
         <v>2700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>300</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,54 +4643,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E100" s="3">
         <v>143900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>141300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>182600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>319100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>28300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>36900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>162600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>80800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>10800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>20900</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4473,70 +4721,76 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E102" s="3">
         <v>77600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-80400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>60900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>22400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>55000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1600</v>
-      </c>
-      <c r="L102" s="3">
-        <v>26100</v>
       </c>
       <c r="M102" s="3">
         <v>26100</v>
       </c>
       <c r="N102" s="3">
+        <v>26100</v>
+      </c>
+      <c r="O102" s="3">
         <v>-4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNWB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>FNWB</t>
   </si>
@@ -656,124 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42185</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41820</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41455</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41090</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E8" s="3">
         <v>50900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>64100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>77200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>72600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>54800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>44200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>41500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>36800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>27500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>25800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>26900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -819,39 +825,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E10" s="3">
         <v>50900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>64100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>77200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>72600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>54800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>44200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -867,9 +876,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,39 +999,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>-800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1031,39 +1050,42 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E15" s="3">
         <v>1400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1600</v>
       </c>
       <c r="J15" s="3">
         <v>1600</v>
       </c>
       <c r="K15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L15" s="3">
         <v>1400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E17" s="3">
         <v>58100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>60100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>61400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>53700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15100</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11800</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,104 +1245,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-23600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-21700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-28300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-15600</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>4900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>-1500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1338,8 +1377,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3800</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1800</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>23600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>21700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>28300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>15600</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42185</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41820</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41455</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41090</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,56 +2159,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E41" s="3">
         <v>72400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>123200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>45600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>126000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>65200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14500</v>
-      </c>
-      <c r="M41" s="3">
-        <v>12800</v>
       </c>
       <c r="N41" s="3">
         <v>12800</v>
       </c>
       <c r="O41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="P41" s="3">
         <v>14200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2131,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2152,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
-        <v>14200</v>
+        <v>0</v>
       </c>
       <c r="M42" s="3">
         <v>14200</v>
@@ -2161,17 +2250,20 @@
         <v>14200</v>
       </c>
       <c r="O42" s="3">
+        <v>14200</v>
+      </c>
+      <c r="P42" s="3">
         <v>14800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>20600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>40900</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2199,8 +2291,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2217,14 +2309,17 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>1400</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>5</v>
@@ -2235,18 +2330,18 @@
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2265,39 +2360,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E45" s="3">
         <v>8200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3700</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2313,39 +2411,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>102400</v>
+        <v>108700</v>
       </c>
       <c r="E46" s="3">
+        <v>97900</v>
+      </c>
+      <c r="F46" s="3">
         <v>152600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>152700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>86800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>62000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>45600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2361,39 +2462,42 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>368000</v>
+        <v>303000</v>
       </c>
       <c r="E47" s="3">
+        <v>372500</v>
+      </c>
+      <c r="F47" s="3">
         <v>324100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>352500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>353000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>370300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>321600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>313400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>347400</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2409,86 +2513,92 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E48" s="3">
         <v>27100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13200</v>
-      </c>
-      <c r="M48" s="3">
-        <v>13500</v>
       </c>
       <c r="N48" s="3">
         <v>13500</v>
       </c>
       <c r="O48" s="3">
+        <v>13500</v>
+      </c>
+      <c r="P48" s="3">
         <v>12300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E49" s="3">
         <v>4400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1100</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1000</v>
       </c>
       <c r="M49" s="3">
         <v>1000</v>
@@ -2497,17 +2607,20 @@
         <v>1000</v>
       </c>
       <c r="O49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P49" s="3">
         <v>1300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1900</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,41 +2717,44 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E52" s="3">
         <v>41200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -2649,9 +2768,12 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2107900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2232000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2201800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2042100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1921100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1654300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1307300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1258800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1215700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1087700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>1010100</v>
       </c>
       <c r="N54" s="3">
         <v>1010100</v>
       </c>
       <c r="O54" s="3">
+        <v>1010100</v>
+      </c>
+      <c r="P54" s="3">
         <v>795300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>784500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>771900</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,37 +2915,38 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1599100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1688000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1676900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1564300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1580600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1333500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1001600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>940300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>885000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
@@ -2825,7 +2955,7 @@
         <v>200</v>
       </c>
       <c r="O57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>300</v>
@@ -2833,39 +2963,42 @@
       <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>300</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>138900</v>
+        <v>117300</v>
       </c>
       <c r="E58" s="3">
+        <v>136600</v>
+      </c>
+      <c r="F58" s="3">
         <v>202500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>167000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>60000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>92900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>91600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>84100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2881,23 +3014,26 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1100</v>
       </c>
       <c r="H59" s="3">
         <v>1100</v>
@@ -2909,59 +3045,62 @@
         <v>1100</v>
       </c>
       <c r="K59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>15200</v>
       </c>
       <c r="N59" s="3">
         <v>15200</v>
       </c>
       <c r="O59" s="3">
+        <v>15200</v>
+      </c>
+      <c r="P59" s="3">
         <v>6400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1862800</v>
+        <v>1741100</v>
       </c>
       <c r="E60" s="3">
+        <v>1860500</v>
+      </c>
+      <c r="F60" s="3">
         <v>1911800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1764400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1611300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1418000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1110500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1041500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>978600</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2977,39 +3116,42 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>214700</v>
+        <v>209000</v>
       </c>
       <c r="E61" s="3">
+        <v>217000</v>
+      </c>
+      <c r="F61" s="3">
         <v>125900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>119400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>119300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>50000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>45000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>60000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3025,9 +3167,12 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3035,11 +3180,11 @@
         <v>600</v>
       </c>
       <c r="E62" s="3">
+        <v>600</v>
+      </c>
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
       <c r="G62" s="3">
         <v>0</v>
       </c>
@@ -3065,17 +3210,20 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>1100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2900</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1950600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2078100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2038500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1883800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1730600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1468000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1130500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1086500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1038600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>910000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>820400</v>
       </c>
       <c r="N66" s="3">
         <v>820400</v>
       </c>
       <c r="O66" s="3">
+        <v>820400</v>
+      </c>
+      <c r="P66" s="3">
         <v>714300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>705900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>694600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E72" s="3">
         <v>97200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>107300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>114400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>103000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>92700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>86200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>81600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>78600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>77500</v>
-      </c>
-      <c r="M72" s="3">
-        <v>77300</v>
       </c>
       <c r="N72" s="3">
         <v>77300</v>
       </c>
       <c r="O72" s="3">
+        <v>77300</v>
+      </c>
+      <c r="P72" s="3">
         <v>79700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>77000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>74700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E76" s="3">
         <v>153900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>163300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>161600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>191000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>176900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>172300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>177000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>177700</v>
-      </c>
-      <c r="M76" s="3">
-        <v>189700</v>
       </c>
       <c r="N76" s="3">
         <v>189700</v>
       </c>
       <c r="O76" s="3">
+        <v>189700</v>
+      </c>
+      <c r="P76" s="3">
         <v>81000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>78600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>77300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42185</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41820</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41455</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41090</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1400</v>
       </c>
       <c r="H83" s="3">
         <v>1400</v>
       </c>
       <c r="I83" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="J83" s="3">
         <v>1300</v>
       </c>
       <c r="K83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>1500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>2300</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
         <v>16900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-1200</v>
       </c>
       <c r="N89" s="3">
         <v>-1200</v>
       </c>
       <c r="O89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P89" s="3">
         <v>3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9900</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1300</v>
       </c>
       <c r="N91" s="3">
         <v>-1300</v>
       </c>
       <c r="O91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>132900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-87100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-84200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-237600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-136900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-316000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-60700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-118000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-80300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-18400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-24100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,35 +4687,36 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E96" s="3">
         <v>2600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,57 +4888,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-117500</v>
+      </c>
+      <c r="E100" s="3">
         <v>19500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>143900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>141300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>182600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>319100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>28300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>36900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>162600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>80800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>10800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>20900</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4724,73 +4972,79 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-50700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>77600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-80400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>60900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1600</v>
-      </c>
-      <c r="M102" s="3">
-        <v>26100</v>
       </c>
       <c r="N102" s="3">
         <v>26100</v>
       </c>
       <c r="O102" s="3">
+        <v>26100</v>
+      </c>
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
